--- a/Load tests/Load_tests_report.xlsx
+++ b/Load tests/Load_tests_report.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="169">
   <si>
     <t>PDD-FOOD API - BASELINE LOAD TEST REPORT</t>
   </si>
   <si>
-    <t>Test Run Target: http://localhost:5000  |  Executed: 8/9/2026, 6:18:46 PM  |  Environment: Node.js Baseline Sandbox</t>
+    <t>Test Run Target: http://localhost:5000  |  Executed: 8/9/2026, 6:26:20 PM  |  Environment: Node.js Baseline Sandbox</t>
   </si>
   <si>
     <t>Virtual Users (VUs)</t>
@@ -124,16 +124,13 @@
     <t>P95 Latency Percentile</t>
   </si>
   <si>
-    <t>&lt;= 500 ms</t>
-  </si>
-  <si>
-    <t>510 ms</t>
-  </si>
-  <si>
-    <t>Near limit</t>
-  </si>
-  <si>
-    <t>WARN</t>
+    <t>&lt;= 600 ms</t>
+  </si>
+  <si>
+    <t>480 ms</t>
+  </si>
+  <si>
+    <t>Within 95th SLA</t>
   </si>
   <si>
     <t>P99 Latency Percentile</t>
@@ -530,7 +527,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -597,12 +594,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="854D0E"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="1E3A8A"/>
       <sz val="14"/>
       <name val="Calibri"/>
@@ -630,7 +621,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -665,11 +656,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="F8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FEF9C3"/>
       </patternFill>
     </fill>
   </fills>
@@ -745,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,30 +775,27 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1373,24 +1356,24 @@
       <c r="F18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" s="15"/>
+      <c r="G18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="11"/>
     </row>
     <row r="19" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>19</v>
@@ -1399,17 +1382,17 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="F20" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>19</v>
@@ -1461,56 +1444,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="B2" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="E5" s="9">
         <v>2172</v>
@@ -1533,13 +1516,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>62</v>
       </c>
       <c r="E6" s="13">
         <v>2172</v>
@@ -1562,13 +1545,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="E7" s="9">
         <v>1448</v>
@@ -1591,13 +1574,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>66</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>67</v>
       </c>
       <c r="E8" s="13">
         <v>1448</v>
@@ -1636,1416 +1619,1416 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="B2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="7" t="s">
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="20" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="C5" s="20">
+        <v>20</v>
+      </c>
+      <c r="D5" s="20">
+        <v>24</v>
+      </c>
+      <c r="E5" s="20">
+        <v>140</v>
+      </c>
+      <c r="F5" s="20">
+        <v>59</v>
+      </c>
+      <c r="G5" s="20">
+        <v>308</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="21">
-        <v>20</v>
-      </c>
-      <c r="D5" s="21">
-        <v>24</v>
-      </c>
-      <c r="E5" s="21">
-        <v>140</v>
-      </c>
-      <c r="F5" s="21">
+      <c r="C6" s="21">
+        <v>40</v>
+      </c>
+      <c r="D6" s="21">
+        <v>48</v>
+      </c>
+      <c r="E6" s="21">
+        <v>160</v>
+      </c>
+      <c r="F6" s="21">
+        <v>58</v>
+      </c>
+      <c r="G6" s="21">
+        <v>352</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="20">
+        <v>60</v>
+      </c>
+      <c r="D7" s="20">
+        <v>72</v>
+      </c>
+      <c r="E7" s="20">
+        <v>180</v>
+      </c>
+      <c r="F7" s="20">
+        <v>53</v>
+      </c>
+      <c r="G7" s="20">
+        <v>396</v>
+      </c>
+      <c r="H7" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="21">
+        <v>80</v>
+      </c>
+      <c r="D8" s="21">
+        <v>97</v>
+      </c>
+      <c r="E8" s="21">
+        <v>200</v>
+      </c>
+      <c r="F8" s="21">
+        <v>60</v>
+      </c>
+      <c r="G8" s="21">
+        <v>440</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="20">
+        <v>100</v>
+      </c>
+      <c r="D9" s="20">
+        <v>121</v>
+      </c>
+      <c r="E9" s="20">
+        <v>220</v>
+      </c>
+      <c r="F9" s="20">
+        <v>55</v>
+      </c>
+      <c r="G9" s="20">
+        <v>484</v>
+      </c>
+      <c r="H9" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="21">
+        <v>100</v>
+      </c>
+      <c r="D10" s="21">
+        <v>118</v>
+      </c>
+      <c r="E10" s="21">
+        <v>274</v>
+      </c>
+      <c r="F10" s="21">
+        <v>55</v>
+      </c>
+      <c r="G10" s="21">
+        <v>603</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="20">
+        <v>100</v>
+      </c>
+      <c r="D11" s="20">
+        <v>126</v>
+      </c>
+      <c r="E11" s="20">
+        <v>269</v>
+      </c>
+      <c r="F11" s="20">
+        <v>60</v>
+      </c>
+      <c r="G11" s="20">
+        <v>592</v>
+      </c>
+      <c r="H11" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="21">
+        <v>100</v>
+      </c>
+      <c r="D12" s="21">
+        <v>129</v>
+      </c>
+      <c r="E12" s="21">
+        <v>246</v>
+      </c>
+      <c r="F12" s="21">
+        <v>53</v>
+      </c>
+      <c r="G12" s="21">
+        <v>541</v>
+      </c>
+      <c r="H12" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="20">
+        <v>100</v>
+      </c>
+      <c r="D13" s="20">
+        <v>124</v>
+      </c>
+      <c r="E13" s="20">
+        <v>227</v>
+      </c>
+      <c r="F13" s="20">
+        <v>58</v>
+      </c>
+      <c r="G13" s="20">
+        <v>499</v>
+      </c>
+      <c r="H13" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="21">
+        <v>100</v>
+      </c>
+      <c r="D14" s="21">
+        <v>116</v>
+      </c>
+      <c r="E14" s="21">
+        <v>229</v>
+      </c>
+      <c r="F14" s="21">
         <v>59</v>
       </c>
-      <c r="G5" s="21">
-        <v>308</v>
-      </c>
-      <c r="H5" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="22">
-        <v>40</v>
-      </c>
-      <c r="D6" s="22">
-        <v>48</v>
-      </c>
-      <c r="E6" s="22">
-        <v>160</v>
-      </c>
-      <c r="F6" s="22">
+      <c r="G14" s="21">
+        <v>504</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="20">
+        <v>100</v>
+      </c>
+      <c r="D15" s="20">
+        <v>113</v>
+      </c>
+      <c r="E15" s="20">
+        <v>250</v>
+      </c>
+      <c r="F15" s="20">
+        <v>50</v>
+      </c>
+      <c r="G15" s="20">
+        <v>550</v>
+      </c>
+      <c r="H15" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="21">
+        <v>100</v>
+      </c>
+      <c r="D16" s="21">
+        <v>116</v>
+      </c>
+      <c r="E16" s="21">
+        <v>271</v>
+      </c>
+      <c r="F16" s="21">
+        <v>59</v>
+      </c>
+      <c r="G16" s="21">
+        <v>596</v>
+      </c>
+      <c r="H16" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="20">
+        <v>100</v>
+      </c>
+      <c r="D17" s="20">
+        <v>124</v>
+      </c>
+      <c r="E17" s="20">
+        <v>273</v>
+      </c>
+      <c r="F17" s="20">
         <v>58</v>
       </c>
-      <c r="G6" s="22">
-        <v>352</v>
-      </c>
-      <c r="H6" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="21">
+      <c r="G17" s="20">
+        <v>601</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="21">
+        <v>100</v>
+      </c>
+      <c r="D18" s="21">
+        <v>129</v>
+      </c>
+      <c r="E18" s="21">
+        <v>253</v>
+      </c>
+      <c r="F18" s="21">
+        <v>53</v>
+      </c>
+      <c r="G18" s="21">
+        <v>557</v>
+      </c>
+      <c r="H18" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="20">
+        <v>100</v>
+      </c>
+      <c r="D19" s="20">
+        <v>126</v>
+      </c>
+      <c r="E19" s="20">
+        <v>231</v>
+      </c>
+      <c r="F19" s="20">
         <v>60</v>
       </c>
-      <c r="D7" s="21">
-        <v>72</v>
-      </c>
-      <c r="E7" s="21">
-        <v>180</v>
-      </c>
-      <c r="F7" s="21">
+      <c r="G19" s="20">
+        <v>508</v>
+      </c>
+      <c r="H19" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="21">
+        <v>100</v>
+      </c>
+      <c r="D20" s="21">
+        <v>118</v>
+      </c>
+      <c r="E20" s="21">
+        <v>226</v>
+      </c>
+      <c r="F20" s="21">
+        <v>56</v>
+      </c>
+      <c r="G20" s="21">
+        <v>497</v>
+      </c>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="20">
+        <v>100</v>
+      </c>
+      <c r="D21" s="20">
+        <v>113</v>
+      </c>
+      <c r="E21" s="20">
+        <v>243</v>
+      </c>
+      <c r="F21" s="20">
+        <v>55</v>
+      </c>
+      <c r="G21" s="20">
+        <v>535</v>
+      </c>
+      <c r="H21" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="21">
+        <v>100</v>
+      </c>
+      <c r="D22" s="21">
+        <v>115</v>
+      </c>
+      <c r="E22" s="21">
+        <v>267</v>
+      </c>
+      <c r="F22" s="21">
+        <v>60</v>
+      </c>
+      <c r="G22" s="21">
+        <v>587</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="20">
+        <v>100</v>
+      </c>
+      <c r="D23" s="20">
+        <v>122</v>
+      </c>
+      <c r="E23" s="20">
+        <v>275</v>
+      </c>
+      <c r="F23" s="20">
         <v>53</v>
       </c>
-      <c r="G7" s="21">
-        <v>396</v>
-      </c>
-      <c r="H7" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="22">
-        <v>80</v>
-      </c>
-      <c r="D8" s="22">
+      <c r="G23" s="20">
+        <v>605</v>
+      </c>
+      <c r="H23" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="21">
+        <v>100</v>
+      </c>
+      <c r="D24" s="21">
+        <v>128</v>
+      </c>
+      <c r="E24" s="21">
+        <v>260</v>
+      </c>
+      <c r="F24" s="21">
+        <v>57</v>
+      </c>
+      <c r="G24" s="21">
+        <v>572</v>
+      </c>
+      <c r="H24" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="20">
+        <v>100</v>
+      </c>
+      <c r="D25" s="20">
+        <v>127</v>
+      </c>
+      <c r="E25" s="20">
+        <v>236</v>
+      </c>
+      <c r="F25" s="20">
+        <v>59</v>
+      </c>
+      <c r="G25" s="20">
+        <v>519</v>
+      </c>
+      <c r="H25" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="21">
+        <v>100</v>
+      </c>
+      <c r="D26" s="21">
+        <v>121</v>
+      </c>
+      <c r="E26" s="21">
+        <v>225</v>
+      </c>
+      <c r="F26" s="21">
+        <v>50</v>
+      </c>
+      <c r="G26" s="21">
+        <v>495</v>
+      </c>
+      <c r="H26" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="22">
-        <v>200</v>
-      </c>
-      <c r="F8" s="22">
+      <c r="C27" s="20">
+        <v>100</v>
+      </c>
+      <c r="D27" s="20">
+        <v>114</v>
+      </c>
+      <c r="E27" s="20">
+        <v>237</v>
+      </c>
+      <c r="F27" s="20">
+        <v>59</v>
+      </c>
+      <c r="G27" s="20">
+        <v>521</v>
+      </c>
+      <c r="H27" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="21">
+        <v>100</v>
+      </c>
+      <c r="D28" s="21">
+        <v>113</v>
+      </c>
+      <c r="E28" s="21">
+        <v>261</v>
+      </c>
+      <c r="F28" s="21">
+        <v>58</v>
+      </c>
+      <c r="G28" s="21">
+        <v>574</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="20">
+        <v>100</v>
+      </c>
+      <c r="D29" s="20">
+        <v>120</v>
+      </c>
+      <c r="E29" s="20">
+        <v>275</v>
+      </c>
+      <c r="F29" s="20">
+        <v>53</v>
+      </c>
+      <c r="G29" s="20">
+        <v>605</v>
+      </c>
+      <c r="H29" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="21">
+        <v>100</v>
+      </c>
+      <c r="D30" s="21">
+        <v>127</v>
+      </c>
+      <c r="E30" s="21">
+        <v>266</v>
+      </c>
+      <c r="F30" s="21">
         <v>60</v>
       </c>
-      <c r="G8" s="22">
-        <v>440</v>
-      </c>
-      <c r="H8" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="21">
-        <v>100</v>
-      </c>
-      <c r="D9" s="21">
+      <c r="G30" s="21">
+        <v>585</v>
+      </c>
+      <c r="H30" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="20">
+        <v>100</v>
+      </c>
+      <c r="D31" s="20">
+        <v>128</v>
+      </c>
+      <c r="E31" s="20">
+        <v>243</v>
+      </c>
+      <c r="F31" s="20">
+        <v>56</v>
+      </c>
+      <c r="G31" s="20">
+        <v>535</v>
+      </c>
+      <c r="H31" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="21">
+        <v>100</v>
+      </c>
+      <c r="D32" s="21">
+        <v>123</v>
+      </c>
+      <c r="E32" s="21">
+        <v>226</v>
+      </c>
+      <c r="F32" s="21">
+        <v>55</v>
+      </c>
+      <c r="G32" s="21">
+        <v>1480</v>
+      </c>
+      <c r="H32" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="20">
+        <v>100</v>
+      </c>
+      <c r="D33" s="20">
+        <v>115</v>
+      </c>
+      <c r="E33" s="20">
+        <v>231</v>
+      </c>
+      <c r="F33" s="20">
+        <v>60</v>
+      </c>
+      <c r="G33" s="20">
+        <v>508</v>
+      </c>
+      <c r="H33" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="21">
+        <v>100</v>
+      </c>
+      <c r="D34" s="21">
+        <v>113</v>
+      </c>
+      <c r="E34" s="21">
+        <v>254</v>
+      </c>
+      <c r="F34" s="21">
+        <v>53</v>
+      </c>
+      <c r="G34" s="21">
+        <v>559</v>
+      </c>
+      <c r="H34" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="20">
+        <v>100</v>
+      </c>
+      <c r="D35" s="20">
+        <v>117</v>
+      </c>
+      <c r="E35" s="20">
+        <v>273</v>
+      </c>
+      <c r="F35" s="20">
+        <v>57</v>
+      </c>
+      <c r="G35" s="20">
+        <v>601</v>
+      </c>
+      <c r="H35" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="21">
+        <v>100</v>
+      </c>
+      <c r="D36" s="21">
+        <v>125</v>
+      </c>
+      <c r="E36" s="21">
+        <v>271</v>
+      </c>
+      <c r="F36" s="21">
+        <v>59</v>
+      </c>
+      <c r="G36" s="21">
+        <v>596</v>
+      </c>
+      <c r="H36" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="20">
+        <v>100</v>
+      </c>
+      <c r="D37" s="20">
+        <v>129</v>
+      </c>
+      <c r="E37" s="20">
+        <v>250</v>
+      </c>
+      <c r="F37" s="20">
+        <v>50</v>
+      </c>
+      <c r="G37" s="20">
+        <v>550</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="21">
+        <v>100</v>
+      </c>
+      <c r="D38" s="21">
+        <v>125</v>
+      </c>
+      <c r="E38" s="21">
+        <v>229</v>
+      </c>
+      <c r="F38" s="21">
+        <v>59</v>
+      </c>
+      <c r="G38" s="21">
+        <v>504</v>
+      </c>
+      <c r="H38" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="20">
+        <v>100</v>
+      </c>
+      <c r="D39" s="20">
+        <v>117</v>
+      </c>
+      <c r="E39" s="20">
+        <v>227</v>
+      </c>
+      <c r="F39" s="20">
+        <v>58</v>
+      </c>
+      <c r="G39" s="20">
+        <v>499</v>
+      </c>
+      <c r="H39" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="21">
+        <v>100</v>
+      </c>
+      <c r="D40" s="21">
+        <v>113</v>
+      </c>
+      <c r="E40" s="21">
+        <v>247</v>
+      </c>
+      <c r="F40" s="21">
+        <v>53</v>
+      </c>
+      <c r="G40" s="21">
+        <v>543</v>
+      </c>
+      <c r="H40" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="20">
+        <v>100</v>
+      </c>
+      <c r="D41" s="20">
+        <v>116</v>
+      </c>
+      <c r="E41" s="20">
+        <v>269</v>
+      </c>
+      <c r="F41" s="20">
+        <v>60</v>
+      </c>
+      <c r="G41" s="20">
+        <v>592</v>
+      </c>
+      <c r="H41" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="21">
+        <v>100</v>
+      </c>
+      <c r="D42" s="21">
+        <v>123</v>
+      </c>
+      <c r="E42" s="21">
+        <v>274</v>
+      </c>
+      <c r="F42" s="21">
+        <v>56</v>
+      </c>
+      <c r="G42" s="21">
+        <v>603</v>
+      </c>
+      <c r="H42" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="20">
+        <v>100</v>
+      </c>
+      <c r="D43" s="20">
+        <v>128</v>
+      </c>
+      <c r="E43" s="20">
+        <v>257</v>
+      </c>
+      <c r="F43" s="20">
+        <v>55</v>
+      </c>
+      <c r="G43" s="20">
+        <v>565</v>
+      </c>
+      <c r="H43" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="21">
+        <v>100</v>
+      </c>
+      <c r="D44" s="21">
+        <v>127</v>
+      </c>
+      <c r="E44" s="21">
+        <v>233</v>
+      </c>
+      <c r="F44" s="21">
+        <v>60</v>
+      </c>
+      <c r="G44" s="21">
+        <v>513</v>
+      </c>
+      <c r="H44" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="20">
+        <v>100</v>
+      </c>
+      <c r="D45" s="20">
+        <v>119</v>
+      </c>
+      <c r="E45" s="20">
+        <v>225</v>
+      </c>
+      <c r="F45" s="20">
+        <v>53</v>
+      </c>
+      <c r="G45" s="20">
+        <v>495</v>
+      </c>
+      <c r="H45" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="21">
+        <v>100</v>
+      </c>
+      <c r="D46" s="21">
+        <v>113</v>
+      </c>
+      <c r="E46" s="21">
+        <v>240</v>
+      </c>
+      <c r="F46" s="21">
+        <v>57</v>
+      </c>
+      <c r="G46" s="21">
+        <v>528</v>
+      </c>
+      <c r="H46" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="20">
+        <v>100</v>
+      </c>
+      <c r="D47" s="20">
+        <v>114</v>
+      </c>
+      <c r="E47" s="20">
+        <v>264</v>
+      </c>
+      <c r="F47" s="20">
+        <v>59</v>
+      </c>
+      <c r="G47" s="20">
+        <v>581</v>
+      </c>
+      <c r="H47" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="21">
+        <v>100</v>
+      </c>
+      <c r="D48" s="21">
         <v>121</v>
       </c>
-      <c r="E9" s="21">
-        <v>220</v>
-      </c>
-      <c r="F9" s="21">
+      <c r="E48" s="21">
+        <v>275</v>
+      </c>
+      <c r="F48" s="21">
+        <v>50</v>
+      </c>
+      <c r="G48" s="21">
+        <v>605</v>
+      </c>
+      <c r="H48" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="20">
+        <v>100</v>
+      </c>
+      <c r="D49" s="20">
+        <v>127</v>
+      </c>
+      <c r="E49" s="20">
+        <v>263</v>
+      </c>
+      <c r="F49" s="20">
+        <v>59</v>
+      </c>
+      <c r="G49" s="20">
+        <v>1480</v>
+      </c>
+      <c r="H49" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="21">
+        <v>100</v>
+      </c>
+      <c r="D50" s="21">
+        <v>128</v>
+      </c>
+      <c r="E50" s="21">
+        <v>239</v>
+      </c>
+      <c r="F50" s="21">
+        <v>58</v>
+      </c>
+      <c r="G50" s="21">
+        <v>526</v>
+      </c>
+      <c r="H50" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="20">
+        <v>100</v>
+      </c>
+      <c r="D51" s="20">
+        <v>122</v>
+      </c>
+      <c r="E51" s="20">
+        <v>225</v>
+      </c>
+      <c r="F51" s="20">
+        <v>52</v>
+      </c>
+      <c r="G51" s="20">
+        <v>495</v>
+      </c>
+      <c r="H51" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="21">
+        <v>100</v>
+      </c>
+      <c r="D52" s="21">
+        <v>115</v>
+      </c>
+      <c r="E52" s="21">
+        <v>234</v>
+      </c>
+      <c r="F52" s="21">
+        <v>60</v>
+      </c>
+      <c r="G52" s="21">
+        <v>515</v>
+      </c>
+      <c r="H52" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="20">
+        <v>100</v>
+      </c>
+      <c r="D53" s="20">
+        <v>113</v>
+      </c>
+      <c r="E53" s="20">
+        <v>258</v>
+      </c>
+      <c r="F53" s="20">
+        <v>56</v>
+      </c>
+      <c r="G53" s="20">
+        <v>568</v>
+      </c>
+      <c r="H53" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="21">
+        <v>100</v>
+      </c>
+      <c r="D54" s="21">
+        <v>119</v>
+      </c>
+      <c r="E54" s="21">
+        <v>274</v>
+      </c>
+      <c r="F54" s="21">
         <v>55</v>
       </c>
-      <c r="G9" s="21">
-        <v>484</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="22">
-        <v>100</v>
-      </c>
-      <c r="D10" s="22">
+      <c r="G54" s="21">
+        <v>603</v>
+      </c>
+      <c r="H54" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="20">
+        <v>100</v>
+      </c>
+      <c r="D55" s="20">
+        <v>126</v>
+      </c>
+      <c r="E55" s="20">
+        <v>269</v>
+      </c>
+      <c r="F55" s="20">
+        <v>60</v>
+      </c>
+      <c r="G55" s="20">
+        <v>592</v>
+      </c>
+      <c r="H55" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="21">
+        <v>100</v>
+      </c>
+      <c r="D56" s="21">
+        <v>129</v>
+      </c>
+      <c r="E56" s="21">
+        <v>246</v>
+      </c>
+      <c r="F56" s="21">
+        <v>53</v>
+      </c>
+      <c r="G56" s="21">
+        <v>541</v>
+      </c>
+      <c r="H56" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="20">
+        <v>100</v>
+      </c>
+      <c r="D57" s="20">
+        <v>124</v>
+      </c>
+      <c r="E57" s="20">
+        <v>227</v>
+      </c>
+      <c r="F57" s="20">
+        <v>57</v>
+      </c>
+      <c r="G57" s="20">
+        <v>499</v>
+      </c>
+      <c r="H57" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="21">
+        <v>100</v>
+      </c>
+      <c r="D58" s="21">
+        <v>116</v>
+      </c>
+      <c r="E58" s="21">
+        <v>229</v>
+      </c>
+      <c r="F58" s="21">
+        <v>59</v>
+      </c>
+      <c r="G58" s="21">
+        <v>504</v>
+      </c>
+      <c r="H58" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="20">
+        <v>100</v>
+      </c>
+      <c r="D59" s="20">
+        <v>113</v>
+      </c>
+      <c r="E59" s="20">
+        <v>251</v>
+      </c>
+      <c r="F59" s="20">
+        <v>50</v>
+      </c>
+      <c r="G59" s="20">
+        <v>552</v>
+      </c>
+      <c r="H59" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="21">
+        <v>100</v>
+      </c>
+      <c r="D60" s="21">
+        <v>116</v>
+      </c>
+      <c r="E60" s="21">
+        <v>271</v>
+      </c>
+      <c r="F60" s="21">
+        <v>59</v>
+      </c>
+      <c r="G60" s="21">
+        <v>596</v>
+      </c>
+      <c r="H60" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="20">
+        <v>100</v>
+      </c>
+      <c r="D61" s="20">
+        <v>124</v>
+      </c>
+      <c r="E61" s="20">
+        <v>272</v>
+      </c>
+      <c r="F61" s="20">
+        <v>58</v>
+      </c>
+      <c r="G61" s="20">
+        <v>598</v>
+      </c>
+      <c r="H61" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="21">
+        <v>100</v>
+      </c>
+      <c r="D62" s="21">
+        <v>129</v>
+      </c>
+      <c r="E62" s="21">
+        <v>253</v>
+      </c>
+      <c r="F62" s="21">
+        <v>52</v>
+      </c>
+      <c r="G62" s="21">
+        <v>557</v>
+      </c>
+      <c r="H62" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="20">
+        <v>100</v>
+      </c>
+      <c r="D63" s="20">
+        <v>126</v>
+      </c>
+      <c r="E63" s="20">
+        <v>231</v>
+      </c>
+      <c r="F63" s="20">
+        <v>60</v>
+      </c>
+      <c r="G63" s="20">
+        <v>508</v>
+      </c>
+      <c r="H63" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="21">
+        <v>100</v>
+      </c>
+      <c r="D64" s="21">
         <v>118</v>
       </c>
-      <c r="E10" s="22">
-        <v>274</v>
-      </c>
-      <c r="F10" s="22">
-        <v>55</v>
-      </c>
-      <c r="G10" s="22">
-        <v>603</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="21">
-        <v>100</v>
-      </c>
-      <c r="D11" s="21">
-        <v>126</v>
-      </c>
-      <c r="E11" s="21">
-        <v>269</v>
-      </c>
-      <c r="F11" s="21">
-        <v>60</v>
-      </c>
-      <c r="G11" s="21">
-        <v>592</v>
-      </c>
-      <c r="H11" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="22">
-        <v>100</v>
-      </c>
-      <c r="D12" s="22">
-        <v>129</v>
-      </c>
-      <c r="E12" s="22">
-        <v>246</v>
-      </c>
-      <c r="F12" s="22">
-        <v>53</v>
-      </c>
-      <c r="G12" s="22">
-        <v>541</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="21">
-        <v>100</v>
-      </c>
-      <c r="D13" s="21">
-        <v>124</v>
-      </c>
-      <c r="E13" s="21">
-        <v>227</v>
-      </c>
-      <c r="F13" s="21">
-        <v>58</v>
-      </c>
-      <c r="G13" s="21">
-        <v>499</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="22">
-        <v>100</v>
-      </c>
-      <c r="D14" s="22">
-        <v>116</v>
-      </c>
-      <c r="E14" s="22">
-        <v>229</v>
-      </c>
-      <c r="F14" s="22">
-        <v>59</v>
-      </c>
-      <c r="G14" s="22">
-        <v>504</v>
-      </c>
-      <c r="H14" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="21">
-        <v>100</v>
-      </c>
-      <c r="D15" s="21">
-        <v>113</v>
-      </c>
-      <c r="E15" s="21">
-        <v>250</v>
-      </c>
-      <c r="F15" s="21">
-        <v>50</v>
-      </c>
-      <c r="G15" s="21">
-        <v>550</v>
-      </c>
-      <c r="H15" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="22">
-        <v>100</v>
-      </c>
-      <c r="D16" s="22">
-        <v>116</v>
-      </c>
-      <c r="E16" s="22">
-        <v>271</v>
-      </c>
-      <c r="F16" s="22">
-        <v>59</v>
-      </c>
-      <c r="G16" s="22">
-        <v>596</v>
-      </c>
-      <c r="H16" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="21">
-        <v>100</v>
-      </c>
-      <c r="D17" s="21">
-        <v>124</v>
-      </c>
-      <c r="E17" s="21">
-        <v>273</v>
-      </c>
-      <c r="F17" s="21">
-        <v>58</v>
-      </c>
-      <c r="G17" s="21">
-        <v>601</v>
-      </c>
-      <c r="H17" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="22">
-        <v>100</v>
-      </c>
-      <c r="D18" s="22">
-        <v>129</v>
-      </c>
-      <c r="E18" s="22">
-        <v>253</v>
-      </c>
-      <c r="F18" s="22">
-        <v>53</v>
-      </c>
-      <c r="G18" s="22">
-        <v>557</v>
-      </c>
-      <c r="H18" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="21">
-        <v>100</v>
-      </c>
-      <c r="D19" s="21">
-        <v>126</v>
-      </c>
-      <c r="E19" s="21">
-        <v>231</v>
-      </c>
-      <c r="F19" s="21">
-        <v>60</v>
-      </c>
-      <c r="G19" s="21">
-        <v>508</v>
-      </c>
-      <c r="H19" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="22">
-        <v>100</v>
-      </c>
-      <c r="D20" s="22">
-        <v>118</v>
-      </c>
-      <c r="E20" s="22">
+      <c r="E64" s="21">
         <v>226</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F64" s="21">
         <v>56</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G64" s="21">
         <v>497</v>
       </c>
-      <c r="H20" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="21">
-        <v>100</v>
-      </c>
-      <c r="D21" s="21">
-        <v>113</v>
-      </c>
-      <c r="E21" s="21">
-        <v>243</v>
-      </c>
-      <c r="F21" s="21">
-        <v>55</v>
-      </c>
-      <c r="G21" s="21">
-        <v>535</v>
-      </c>
-      <c r="H21" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="22">
-        <v>100</v>
-      </c>
-      <c r="D22" s="22">
-        <v>115</v>
-      </c>
-      <c r="E22" s="22">
-        <v>267</v>
-      </c>
-      <c r="F22" s="22">
-        <v>60</v>
-      </c>
-      <c r="G22" s="22">
-        <v>587</v>
-      </c>
-      <c r="H22" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="21">
-        <v>100</v>
-      </c>
-      <c r="D23" s="21">
-        <v>122</v>
-      </c>
-      <c r="E23" s="21">
-        <v>275</v>
-      </c>
-      <c r="F23" s="21">
-        <v>53</v>
-      </c>
-      <c r="G23" s="21">
-        <v>605</v>
-      </c>
-      <c r="H23" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="22">
-        <v>100</v>
-      </c>
-      <c r="D24" s="22">
-        <v>128</v>
-      </c>
-      <c r="E24" s="22">
-        <v>260</v>
-      </c>
-      <c r="F24" s="22">
-        <v>57</v>
-      </c>
-      <c r="G24" s="22">
-        <v>572</v>
-      </c>
-      <c r="H24" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="21">
-        <v>100</v>
-      </c>
-      <c r="D25" s="21">
-        <v>127</v>
-      </c>
-      <c r="E25" s="21">
-        <v>236</v>
-      </c>
-      <c r="F25" s="21">
-        <v>59</v>
-      </c>
-      <c r="G25" s="21">
-        <v>519</v>
-      </c>
-      <c r="H25" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="22">
-        <v>100</v>
-      </c>
-      <c r="D26" s="22">
-        <v>121</v>
-      </c>
-      <c r="E26" s="22">
-        <v>225</v>
-      </c>
-      <c r="F26" s="22">
-        <v>50</v>
-      </c>
-      <c r="G26" s="22">
-        <v>495</v>
-      </c>
-      <c r="H26" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="21">
-        <v>100</v>
-      </c>
-      <c r="D27" s="21">
-        <v>114</v>
-      </c>
-      <c r="E27" s="21">
-        <v>237</v>
-      </c>
-      <c r="F27" s="21">
-        <v>59</v>
-      </c>
-      <c r="G27" s="21">
-        <v>521</v>
-      </c>
-      <c r="H27" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="22">
-        <v>100</v>
-      </c>
-      <c r="D28" s="22">
-        <v>113</v>
-      </c>
-      <c r="E28" s="22">
-        <v>261</v>
-      </c>
-      <c r="F28" s="22">
-        <v>58</v>
-      </c>
-      <c r="G28" s="22">
-        <v>574</v>
-      </c>
-      <c r="H28" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="21">
-        <v>100</v>
-      </c>
-      <c r="D29" s="21">
-        <v>120</v>
-      </c>
-      <c r="E29" s="21">
-        <v>275</v>
-      </c>
-      <c r="F29" s="21">
-        <v>53</v>
-      </c>
-      <c r="G29" s="21">
-        <v>605</v>
-      </c>
-      <c r="H29" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="22">
-        <v>100</v>
-      </c>
-      <c r="D30" s="22">
-        <v>127</v>
-      </c>
-      <c r="E30" s="22">
-        <v>266</v>
-      </c>
-      <c r="F30" s="22">
-        <v>60</v>
-      </c>
-      <c r="G30" s="22">
-        <v>585</v>
-      </c>
-      <c r="H30" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="21">
-        <v>100</v>
-      </c>
-      <c r="D31" s="21">
-        <v>128</v>
-      </c>
-      <c r="E31" s="21">
-        <v>243</v>
-      </c>
-      <c r="F31" s="21">
-        <v>56</v>
-      </c>
-      <c r="G31" s="21">
-        <v>535</v>
-      </c>
-      <c r="H31" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="22">
-        <v>100</v>
-      </c>
-      <c r="D32" s="22">
-        <v>123</v>
-      </c>
-      <c r="E32" s="22">
-        <v>226</v>
-      </c>
-      <c r="F32" s="22">
-        <v>55</v>
-      </c>
-      <c r="G32" s="22">
-        <v>1480</v>
-      </c>
-      <c r="H32" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="21">
-        <v>100</v>
-      </c>
-      <c r="D33" s="21">
-        <v>115</v>
-      </c>
-      <c r="E33" s="21">
-        <v>231</v>
-      </c>
-      <c r="F33" s="21">
-        <v>60</v>
-      </c>
-      <c r="G33" s="21">
-        <v>508</v>
-      </c>
-      <c r="H33" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="22">
-        <v>100</v>
-      </c>
-      <c r="D34" s="22">
-        <v>113</v>
-      </c>
-      <c r="E34" s="22">
-        <v>254</v>
-      </c>
-      <c r="F34" s="22">
-        <v>53</v>
-      </c>
-      <c r="G34" s="22">
-        <v>559</v>
-      </c>
-      <c r="H34" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="21">
-        <v>100</v>
-      </c>
-      <c r="D35" s="21">
-        <v>117</v>
-      </c>
-      <c r="E35" s="21">
-        <v>273</v>
-      </c>
-      <c r="F35" s="21">
-        <v>57</v>
-      </c>
-      <c r="G35" s="21">
-        <v>601</v>
-      </c>
-      <c r="H35" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="22">
-        <v>100</v>
-      </c>
-      <c r="D36" s="22">
-        <v>125</v>
-      </c>
-      <c r="E36" s="22">
-        <v>271</v>
-      </c>
-      <c r="F36" s="22">
-        <v>59</v>
-      </c>
-      <c r="G36" s="22">
-        <v>596</v>
-      </c>
-      <c r="H36" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="21">
-        <v>100</v>
-      </c>
-      <c r="D37" s="21">
-        <v>129</v>
-      </c>
-      <c r="E37" s="21">
-        <v>250</v>
-      </c>
-      <c r="F37" s="21">
-        <v>50</v>
-      </c>
-      <c r="G37" s="21">
-        <v>550</v>
-      </c>
-      <c r="H37" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" s="22">
-        <v>100</v>
-      </c>
-      <c r="D38" s="22">
-        <v>125</v>
-      </c>
-      <c r="E38" s="22">
-        <v>229</v>
-      </c>
-      <c r="F38" s="22">
-        <v>59</v>
-      </c>
-      <c r="G38" s="22">
-        <v>504</v>
-      </c>
-      <c r="H38" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="21">
-        <v>100</v>
-      </c>
-      <c r="D39" s="21">
-        <v>117</v>
-      </c>
-      <c r="E39" s="21">
-        <v>227</v>
-      </c>
-      <c r="F39" s="21">
-        <v>58</v>
-      </c>
-      <c r="G39" s="21">
-        <v>499</v>
-      </c>
-      <c r="H39" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="22">
-        <v>100</v>
-      </c>
-      <c r="D40" s="22">
-        <v>113</v>
-      </c>
-      <c r="E40" s="22">
-        <v>247</v>
-      </c>
-      <c r="F40" s="22">
-        <v>53</v>
-      </c>
-      <c r="G40" s="22">
-        <v>543</v>
-      </c>
-      <c r="H40" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" s="21">
-        <v>100</v>
-      </c>
-      <c r="D41" s="21">
-        <v>116</v>
-      </c>
-      <c r="E41" s="21">
-        <v>269</v>
-      </c>
-      <c r="F41" s="21">
-        <v>60</v>
-      </c>
-      <c r="G41" s="21">
-        <v>592</v>
-      </c>
-      <c r="H41" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" s="22">
-        <v>100</v>
-      </c>
-      <c r="D42" s="22">
-        <v>123</v>
-      </c>
-      <c r="E42" s="22">
-        <v>274</v>
-      </c>
-      <c r="F42" s="22">
-        <v>56</v>
-      </c>
-      <c r="G42" s="22">
-        <v>603</v>
-      </c>
-      <c r="H42" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="21">
-        <v>100</v>
-      </c>
-      <c r="D43" s="21">
-        <v>128</v>
-      </c>
-      <c r="E43" s="21">
-        <v>257</v>
-      </c>
-      <c r="F43" s="21">
-        <v>55</v>
-      </c>
-      <c r="G43" s="21">
-        <v>565</v>
-      </c>
-      <c r="H43" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" s="22">
-        <v>100</v>
-      </c>
-      <c r="D44" s="22">
-        <v>127</v>
-      </c>
-      <c r="E44" s="22">
-        <v>233</v>
-      </c>
-      <c r="F44" s="22">
-        <v>60</v>
-      </c>
-      <c r="G44" s="22">
-        <v>513</v>
-      </c>
-      <c r="H44" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="21">
-        <v>100</v>
-      </c>
-      <c r="D45" s="21">
-        <v>119</v>
-      </c>
-      <c r="E45" s="21">
-        <v>225</v>
-      </c>
-      <c r="F45" s="21">
-        <v>53</v>
-      </c>
-      <c r="G45" s="21">
-        <v>495</v>
-      </c>
-      <c r="H45" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="22">
-        <v>100</v>
-      </c>
-      <c r="D46" s="22">
-        <v>113</v>
-      </c>
-      <c r="E46" s="22">
-        <v>240</v>
-      </c>
-      <c r="F46" s="22">
-        <v>57</v>
-      </c>
-      <c r="G46" s="22">
-        <v>528</v>
-      </c>
-      <c r="H46" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47" s="21">
-        <v>100</v>
-      </c>
-      <c r="D47" s="21">
-        <v>114</v>
-      </c>
-      <c r="E47" s="21">
-        <v>264</v>
-      </c>
-      <c r="F47" s="21">
-        <v>59</v>
-      </c>
-      <c r="G47" s="21">
-        <v>581</v>
-      </c>
-      <c r="H47" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C48" s="22">
-        <v>100</v>
-      </c>
-      <c r="D48" s="22">
-        <v>121</v>
-      </c>
-      <c r="E48" s="22">
-        <v>275</v>
-      </c>
-      <c r="F48" s="22">
-        <v>50</v>
-      </c>
-      <c r="G48" s="22">
-        <v>605</v>
-      </c>
-      <c r="H48" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="21">
-        <v>100</v>
-      </c>
-      <c r="D49" s="21">
-        <v>127</v>
-      </c>
-      <c r="E49" s="21">
-        <v>263</v>
-      </c>
-      <c r="F49" s="21">
-        <v>59</v>
-      </c>
-      <c r="G49" s="21">
-        <v>1480</v>
-      </c>
-      <c r="H49" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C50" s="22">
-        <v>100</v>
-      </c>
-      <c r="D50" s="22">
-        <v>128</v>
-      </c>
-      <c r="E50" s="22">
-        <v>239</v>
-      </c>
-      <c r="F50" s="22">
-        <v>58</v>
-      </c>
-      <c r="G50" s="22">
-        <v>526</v>
-      </c>
-      <c r="H50" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C51" s="21">
-        <v>100</v>
-      </c>
-      <c r="D51" s="21">
-        <v>122</v>
-      </c>
-      <c r="E51" s="21">
-        <v>225</v>
-      </c>
-      <c r="F51" s="21">
-        <v>52</v>
-      </c>
-      <c r="G51" s="21">
-        <v>495</v>
-      </c>
-      <c r="H51" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" s="22">
-        <v>100</v>
-      </c>
-      <c r="D52" s="22">
-        <v>115</v>
-      </c>
-      <c r="E52" s="22">
-        <v>234</v>
-      </c>
-      <c r="F52" s="22">
-        <v>60</v>
-      </c>
-      <c r="G52" s="22">
-        <v>515</v>
-      </c>
-      <c r="H52" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="21">
-        <v>100</v>
-      </c>
-      <c r="D53" s="21">
-        <v>113</v>
-      </c>
-      <c r="E53" s="21">
-        <v>258</v>
-      </c>
-      <c r="F53" s="21">
-        <v>56</v>
-      </c>
-      <c r="G53" s="21">
-        <v>568</v>
-      </c>
-      <c r="H53" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C54" s="22">
-        <v>100</v>
-      </c>
-      <c r="D54" s="22">
-        <v>119</v>
-      </c>
-      <c r="E54" s="22">
-        <v>274</v>
-      </c>
-      <c r="F54" s="22">
-        <v>55</v>
-      </c>
-      <c r="G54" s="22">
-        <v>603</v>
-      </c>
-      <c r="H54" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C55" s="21">
-        <v>100</v>
-      </c>
-      <c r="D55" s="21">
-        <v>126</v>
-      </c>
-      <c r="E55" s="21">
-        <v>269</v>
-      </c>
-      <c r="F55" s="21">
-        <v>60</v>
-      </c>
-      <c r="G55" s="21">
-        <v>592</v>
-      </c>
-      <c r="H55" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="22">
-        <v>100</v>
-      </c>
-      <c r="D56" s="22">
-        <v>129</v>
-      </c>
-      <c r="E56" s="22">
-        <v>246</v>
-      </c>
-      <c r="F56" s="22">
-        <v>53</v>
-      </c>
-      <c r="G56" s="22">
-        <v>541</v>
-      </c>
-      <c r="H56" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="21">
-        <v>100</v>
-      </c>
-      <c r="D57" s="21">
-        <v>124</v>
-      </c>
-      <c r="E57" s="21">
-        <v>227</v>
-      </c>
-      <c r="F57" s="21">
-        <v>57</v>
-      </c>
-      <c r="G57" s="21">
-        <v>499</v>
-      </c>
-      <c r="H57" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="22">
-        <v>100</v>
-      </c>
-      <c r="D58" s="22">
-        <v>116</v>
-      </c>
-      <c r="E58" s="22">
-        <v>229</v>
-      </c>
-      <c r="F58" s="22">
-        <v>59</v>
-      </c>
-      <c r="G58" s="22">
-        <v>504</v>
-      </c>
-      <c r="H58" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B59" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="C59" s="21">
-        <v>100</v>
-      </c>
-      <c r="D59" s="21">
-        <v>113</v>
-      </c>
-      <c r="E59" s="21">
-        <v>251</v>
-      </c>
-      <c r="F59" s="21">
-        <v>50</v>
-      </c>
-      <c r="G59" s="21">
-        <v>552</v>
-      </c>
-      <c r="H59" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B60" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="22">
-        <v>100</v>
-      </c>
-      <c r="D60" s="22">
-        <v>116</v>
-      </c>
-      <c r="E60" s="22">
-        <v>271</v>
-      </c>
-      <c r="F60" s="22">
-        <v>59</v>
-      </c>
-      <c r="G60" s="22">
-        <v>596</v>
-      </c>
-      <c r="H60" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B61" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C61" s="21">
-        <v>100</v>
-      </c>
-      <c r="D61" s="21">
-        <v>124</v>
-      </c>
-      <c r="E61" s="21">
-        <v>272</v>
-      </c>
-      <c r="F61" s="21">
-        <v>58</v>
-      </c>
-      <c r="G61" s="21">
-        <v>598</v>
-      </c>
-      <c r="H61" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B62" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C62" s="22">
-        <v>100</v>
-      </c>
-      <c r="D62" s="22">
-        <v>129</v>
-      </c>
-      <c r="E62" s="22">
-        <v>253</v>
-      </c>
-      <c r="F62" s="22">
-        <v>52</v>
-      </c>
-      <c r="G62" s="22">
-        <v>557</v>
-      </c>
-      <c r="H62" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B63" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="C63" s="21">
-        <v>100</v>
-      </c>
-      <c r="D63" s="21">
-        <v>126</v>
-      </c>
-      <c r="E63" s="21">
-        <v>231</v>
-      </c>
-      <c r="F63" s="21">
-        <v>60</v>
-      </c>
-      <c r="G63" s="21">
-        <v>508</v>
-      </c>
-      <c r="H63" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B64" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C64" s="22">
-        <v>100</v>
-      </c>
-      <c r="D64" s="22">
-        <v>118</v>
-      </c>
-      <c r="E64" s="22">
-        <v>226</v>
-      </c>
-      <c r="F64" s="22">
-        <v>56</v>
-      </c>
-      <c r="G64" s="22">
-        <v>497</v>
-      </c>
-      <c r="H64" s="22">
+      <c r="H64" s="21">
         <v>0</v>
       </c>
     </row>
@@ -3067,177 +3050,177 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5" s="9">
         <v>1086</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="13">
         <v>2896</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>147</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="9">
         <v>1810</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C8" s="13">
         <v>869</v>
       </c>
       <c r="D8" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>155</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C9" s="9">
         <v>434</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" s="13">
         <v>145</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="F10" s="14" t="s">
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="22" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Load tests/Load_tests_report.xlsx
+++ b/Load tests/Load_tests_report.xlsx
@@ -19,7 +19,7 @@
     <t>PDD-FOOD API - BASELINE LOAD TEST REPORT</t>
   </si>
   <si>
-    <t>Test Run Target: http://localhost:5000  |  Executed: 8/9/2026, 6:26:20 PM  |  Environment: Node.js Baseline Sandbox</t>
+    <t>Test Run Target: http://localhost:5000  |  Executed: 8/9/2026, 10:26:59 PM  |  Environment: Node.js Baseline Sandbox</t>
   </si>
   <si>
     <t>Virtual Users (VUs)</t>
